--- a/test/excel/keep/struct-open/wide-insert-cols-in.xlsx
+++ b/test/excel/keep/struct-open/wide-insert-cols-in.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mike/Library/Containers/com.microsoft.Excel/Data/tmp/fkeep-62166/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mike/Library/Containers/com.microsoft.Excel/Data/tmp/fkeep-20228/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61754F50-6BAC-0147-9096-4ED3240C7F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EC16E3BC-E2BC-BA46-9161-BBD85CE1FA71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -316,8 +316,8 @@
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>139700</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1206500</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
